--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -656,403 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8900</v>
+      </c>
+      <c r="F8" s="3">
         <v>10300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>12700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>16100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>23500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>18700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>7900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>3500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>8900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>10400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>11300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>9800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F9" s="3">
         <v>6700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>6600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>5700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>10500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>7000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>8200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>7500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>12300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>4300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>4000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>8400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>8400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>10300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>13300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>9100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>7700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>7800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>8200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>15300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-6000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-5800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1110,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1201,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,43 +1296,49 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>5300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1306,26 +1346,26 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>5000</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="3">
-        <v>2900</v>
+        <v>5000</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>2900</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1333,26 +1373,32 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1486,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F17" s="3">
         <v>8300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>13400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>11700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>9500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>13400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>8100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>10000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>6900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>11800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>10100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>8800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>9100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>9300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>9500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>2000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>5300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-700</v>
       </c>
       <c r="W18" s="3">
         <v>-800</v>
       </c>
       <c r="X18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>2200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,26 +1747,28 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1711,50 +1779,50 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1770,97 +1838,109 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F21" s="3">
         <v>2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>14000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>5500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-5100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-200</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-600</v>
       </c>
       <c r="W21" s="3">
         <v>-600</v>
       </c>
       <c r="X21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2500</v>
       </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1894,48 +1974,48 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
@@ -1948,186 +2028,204 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>14000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>5400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
-      </c>
-      <c r="P23" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-5200</v>
       </c>
       <c r="R23" s="3">
         <v>700</v>
       </c>
       <c r="S23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="T23" s="3">
+        <v>700</v>
+      </c>
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="I24" s="3">
+        <v>900</v>
+      </c>
+      <c r="J24" s="3">
         <v>-700</v>
       </c>
-      <c r="E24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="G24" s="3">
-        <v>900</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>16600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>10000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2520,18 +2642,18 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
@@ -2539,28 +2661,28 @@
         <v>0</v>
       </c>
       <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>5200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>1400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>700</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>2800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2571,8 +2693,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,26 +2883,32 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2779,50 +2919,50 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2838,97 +2978,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>16600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>10000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>5400</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>16600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>10000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>5400</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F41" s="3">
         <v>21800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>20000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>12400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>12900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>15900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>27300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>30300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>23300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>24800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>15700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>17100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>17500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>14200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>12600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>15600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>13300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>14000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>15100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>10900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>13900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>13800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>11800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>10800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3623,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3499,130 +3685,142 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>5700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>5900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>6900</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>6400</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>5900</v>
       </c>
       <c r="AC43" s="3">
         <v>6400</v>
       </c>
       <c r="AD43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="AF43" s="3">
         <v>7200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>63900</v>
+      </c>
+      <c r="F44" s="3">
         <v>63400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>65600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>70700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>70000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>68600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>67200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>64800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>61800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>61300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>55600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>55600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>53900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>57200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>53400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>54100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>54200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>55500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>57800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>58700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>59000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>59200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>58900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>58300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>55900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>55400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>56100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>57200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3710,8 +3908,14 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3799,186 +4003,204 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>5000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>9000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>9000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>300</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
         <v>100</v>
       </c>
       <c r="Q47" s="3">
+        <v>300</v>
+      </c>
+      <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3">
-        <v>300</v>
-      </c>
       <c r="S47" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T47" s="3">
         <v>300</v>
       </c>
       <c r="U47" s="3">
+        <v>300</v>
+      </c>
+      <c r="V47" s="3">
+        <v>300</v>
+      </c>
+      <c r="W47" s="3">
         <v>17500</v>
-      </c>
-      <c r="V47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="W47" s="3">
-        <v>9700</v>
       </c>
       <c r="X47" s="3">
         <v>9700</v>
       </c>
       <c r="Y47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AA47" s="3">
         <v>18500</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
         <v>200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>18300</v>
+      </c>
+      <c r="F48" s="3">
         <v>17900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>15100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>10400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>11200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>11200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>13700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>19000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>18600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>17700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>17000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>17100</v>
       </c>
-      <c r="U48" s="3" t="s">
+      <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>9000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>9200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>9500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>9700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>19700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>20000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>20300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>20600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>20700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E52" s="3">
         <v>13500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G52" s="3">
         <v>14800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>16600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>6800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>7000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>11100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>11600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>11600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>4800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>5000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>17400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>8700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>8700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>9500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>10700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>117800</v>
+      </c>
+      <c r="F54" s="3">
         <v>116900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>115900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>113100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>96200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>96800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>94900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>105100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>104900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>101100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>97400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>95900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>95700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>100000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>96700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>97300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>95600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>100100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>100500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>104500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>104600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>106700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>106200</v>
-      </c>
-      <c r="Z54" s="3">
-        <v>105800</v>
-      </c>
-      <c r="AA54" s="3">
-        <v>107000</v>
       </c>
       <c r="AB54" s="3">
         <v>105800</v>
       </c>
       <c r="AC54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AD54" s="3">
+        <v>105800</v>
+      </c>
+      <c r="AE54" s="3">
         <v>106700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>109500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,97 +4837,105 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1300</v>
       </c>
       <c r="O57" s="3">
         <v>2000</v>
       </c>
       <c r="P57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>3500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>7800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>8400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>9200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>6500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>7000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4755,55 +5023,61 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>7400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
@@ -4817,35 +5091,41 @@
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
       <c r="AA59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
         <v>500</v>
       </c>
       <c r="AD59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4933,8 +5213,14 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4945,74 +5231,74 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>600</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5022,25 +5308,31 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
@@ -5052,67 +5344,73 @@
         <v>0</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>6400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>6400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>6900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>7000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>9000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>14400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>9700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>10800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>10700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>11000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>13700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>11500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>10800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>10400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>8500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>12500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>7000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>10700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>16500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>16900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>19700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>19100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>21200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>20300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>19500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>21800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>25600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>79200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>79100</v>
+      </c>
+      <c r="F72" s="3">
         <v>78000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>76600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>76900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>60400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>56700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>54800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>53600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>52700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>49300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>47700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>43800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>44500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>43700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>43100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>47000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>46700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>48900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>49100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>47600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>47600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>47100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>47500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>45600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>48500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>48200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>46800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>47700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>113500</v>
+      </c>
+      <c r="F76" s="3">
         <v>112400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>111000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>107400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>89000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>85300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>83200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>95200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>94100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>90700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>88900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>83400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>82000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>85400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>84600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>90400</v>
-      </c>
-      <c r="S76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="T76" s="3">
-        <v>89900</v>
       </c>
       <c r="U76" s="3">
         <v>89800</v>
       </c>
       <c r="V76" s="3">
+        <v>89900</v>
+      </c>
+      <c r="W76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="X76" s="3">
         <v>88000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>87800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>87000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>87100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>84600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>86700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>86400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>84800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>83900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2800</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>16600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>10000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>5400</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6633,25 +7031,25 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -6663,25 +7061,25 @@
         <v>100</v>
       </c>
       <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
+        <v>100</v>
+      </c>
+      <c r="W83" s="3">
         <v>-200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>300</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
       </c>
       <c r="Y83" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="Z83" s="3">
         <v>300</v>
       </c>
       <c r="AA83" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="AB83" s="3">
         <v>300</v>
@@ -6693,10 +7091,16 @@
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>14100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>7400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>11200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,16 +7702,18 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -7280,20 +7722,20 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -7331,28 +7773,34 @@
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,16 +7983,22 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-5100</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -7547,23 +8007,23 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -7586,40 +8046,46 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8493,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8016,88 +8508,94 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-25600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>1800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>600</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8683,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="F102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>7600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-11600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>7100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>3000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>2200</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -656,429 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F8" s="3">
         <v>12700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>10300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>12700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>16100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>23500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>16100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>18700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>9300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>8900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>10400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>11300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>8900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>9800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F9" s="3">
         <v>10900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>6300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>6700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>5700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>10500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>7000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>8200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>10500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>7500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>12300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>6600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>8400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>8400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>10300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>13300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>9100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>7700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>7800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>8200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>2600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>3600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>15300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>5600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>3500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1137,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1234,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,8 +1335,14 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1316,35 +1355,35 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>5300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1352,26 +1391,26 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>5000</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U14" s="3">
-        <v>2900</v>
+        <v>5000</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>2900</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1379,26 +1418,32 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>200</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1492,8 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1575,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F17" s="3">
         <v>12800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>8300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>13400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>11700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>9500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>11800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>13400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>8100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>10000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>6900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>4300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>11800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>10100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>8800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>9100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>9300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>14000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>5300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-5200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-400</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-700</v>
       </c>
       <c r="Y18" s="3">
         <v>-800</v>
       </c>
       <c r="Z18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1814,10 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1758,23 +1825,23 @@
         <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>400</v>
+      </c>
+      <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1785,50 +1852,50 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1844,126 +1911,138 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>14000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-200</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-600</v>
       </c>
       <c r="Y21" s="3">
         <v>-600</v>
       </c>
       <c r="Z21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>2500</v>
       </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -1980,48 +2059,48 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2034,198 +2113,216 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>4500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>14000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>4400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>5400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
-      </c>
-      <c r="R23" s="3">
-        <v>700</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-5200</v>
       </c>
       <c r="T23" s="3">
         <v>700</v>
       </c>
       <c r="U23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="V23" s="3">
+        <v>700</v>
+      </c>
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E24" s="3">
+        <v>900</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-15200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2416,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>16600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>16600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2719,14 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2648,18 +2769,18 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
@@ -2667,28 +2788,28 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>5200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>1400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>2800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-3100</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2699,8 +2820,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2921,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +3022,14 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2898,23 +3037,23 @@
         <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2925,50 +3064,50 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2984,103 +3123,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>16600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>5400</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3325,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>16600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>5400</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3573,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3610,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F41" s="3">
         <v>18000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>16700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>21800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>20000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>12400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>15900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>15700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>27300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>30300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>23300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>24800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>17100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>17500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>14200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>14200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>14000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>15100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>10900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>13800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>13100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>11800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>10800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,8 +3808,14 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3691,136 +3876,148 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>5700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>5900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>5900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>6900</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>6400</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>5900</v>
       </c>
       <c r="AE43" s="3">
         <v>6400</v>
       </c>
       <c r="AF43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="AH43" s="3">
         <v>7200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F44" s="3">
         <v>68100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>63900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>63400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>65600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>70700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>70000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>68600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>67200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>64800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>61800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>61300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>55600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>55600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>53900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>57200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>53400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>54100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>54200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>55500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>57800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>58700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>59000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>59200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>58900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>58300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>55900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>55400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>56100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>57200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3914,8 +4111,14 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,198 +4212,216 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>5000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>5000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>9000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>9000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>300</v>
       </c>
       <c r="M47" s="3">
         <v>100</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
       </c>
       <c r="S47" s="3">
+        <v>300</v>
+      </c>
+      <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="T47" s="3">
-        <v>300</v>
-      </c>
       <c r="U47" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V47" s="3">
         <v>300</v>
       </c>
       <c r="W47" s="3">
+        <v>300</v>
+      </c>
+      <c r="X47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y47" s="3">
         <v>17500</v>
-      </c>
-      <c r="X47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>9700</v>
       </c>
       <c r="Z47" s="3">
         <v>9700</v>
       </c>
       <c r="AA47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AC47" s="3">
         <v>18500</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AE47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
         <v>200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F48" s="3">
         <v>14100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>18300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>15100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>10400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>11200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>11200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>13600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>13700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>19000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>19100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>18900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>18600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>17700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>17000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>17100</v>
       </c>
-      <c r="W48" s="3" t="s">
+      <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>9000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>9200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>9500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>9700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>19700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>20000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>20300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>20600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>20700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4294,8 +4515,14 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4616,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4717,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F52" s="3">
         <v>13400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>13500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>14800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>16600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>5700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>6500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>6800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>7000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>11100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>11600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>11600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>5500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>4800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>4800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>5000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>17400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>4800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>8700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>8700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>9500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>10700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4919,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>122800</v>
+      </c>
+      <c r="F54" s="3">
         <v>119000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>117800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>116900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>115900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>113100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>96200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>96800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>94900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>105100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>104900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>101100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>97400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>95900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>95700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>100000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>96700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>97300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>95600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>100100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>100500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>104500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>104600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>106700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>106200</v>
-      </c>
-      <c r="AB54" s="3">
-        <v>105800</v>
-      </c>
-      <c r="AC54" s="3">
-        <v>107000</v>
       </c>
       <c r="AD54" s="3">
         <v>105800</v>
       </c>
       <c r="AE54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AF54" s="3">
+        <v>105800</v>
+      </c>
+      <c r="AG54" s="3">
         <v>106700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>109500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +5061,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +5098,111 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1300</v>
       </c>
       <c r="Q57" s="3">
         <v>2000</v>
       </c>
       <c r="R57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>3000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>7800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>8400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>6500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>7000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5029,61 +5296,67 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F59" s="3">
         <v>2600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>7400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>6200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
@@ -5097,35 +5370,41 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
       <c r="AC59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
         <v>500</v>
       </c>
       <c r="AF59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,8 +5498,14 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5237,74 +5522,74 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>6400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>5200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>5800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>5500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>3900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>600</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
@@ -5314,8 +5599,14 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5350,67 +5641,73 @@
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>5000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>5000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>6400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>6400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>7000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>9000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>14400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>9700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>10800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>10700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>11000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>13700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5801,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5902,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +6003,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F66" s="3">
         <v>5200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>10800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>10400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>8500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>12500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>7000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>5800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>10200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>16500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>16900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>19700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>19100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>21200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>20300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>19500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>21800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>25600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +6145,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6242,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6343,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6444,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6545,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>83300</v>
+      </c>
+      <c r="F72" s="3">
         <v>79200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>79100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>78000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>76600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>76900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>60400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>56700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>54800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>53600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>52700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>49300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>47700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>43800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>44500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>43700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>43100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>47000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>46700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>48900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>49100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>47600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>47600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>47100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>47500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>45600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>48500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>48200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>46800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>47700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6747,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6848,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6949,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>118100</v>
+      </c>
+      <c r="F76" s="3">
         <v>113800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>113500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>112400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>111000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>107400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>89000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>85300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>83200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>95200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>94100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>90700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>88900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>83400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>82000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>85400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>84600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>90400</v>
-      </c>
-      <c r="U76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="V76" s="3">
-        <v>89900</v>
       </c>
       <c r="W76" s="3">
         <v>89800</v>
       </c>
       <c r="X76" s="3">
+        <v>89900</v>
+      </c>
+      <c r="Y76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="Z76" s="3">
         <v>88000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>87800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>87000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>87100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>84600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>86700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>86400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>84800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>83900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +7151,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>16600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>5400</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7399,10 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7037,25 +7434,25 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
       <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>200</v>
       </c>
       <c r="T83" s="3">
         <v>100</v>
@@ -7067,25 +7464,25 @@
         <v>100</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>-200</v>
-      </c>
-      <c r="X83" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>300</v>
       </c>
       <c r="Z83" s="3">
         <v>300</v>
       </c>
       <c r="AA83" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="AB83" s="3">
         <v>300</v>
       </c>
       <c r="AC83" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="AD83" s="3">
         <v>300</v>
@@ -7097,10 +7494,16 @@
         <v>300</v>
       </c>
       <c r="AG83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7597,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7698,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7799,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7900,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +8001,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F89" s="3">
         <v>1500</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>7800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>14100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>11200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>1300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>2800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,22 +8143,24 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -7728,20 +8169,20 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7779,28 +8220,34 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8341,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,23 +8442,29 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
@@ -8013,23 +8472,23 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-1200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
@@ -8052,40 +8511,46 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8584,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8681,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8782,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8883,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8984,14 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8514,88 +9005,94 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-25600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8689,99 +9186,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F102" s="3">
         <v>1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-5100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>7600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-3000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-11600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>9400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-3000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1700</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>2200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -905,8 +905,8 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>12500</v>
       </c>
       <c r="E9" s="3">
         <v>13000</v>
@@ -1006,8 +1006,8 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>6600</v>
       </c>
       <c r="E10" s="3">
         <v>6500</v>
@@ -1365,7 +1365,7 @@
         <v>5300</v>
       </c>
       <c r="J14" s="3">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
@@ -1598,10 +1598,10 @@
         <v>8300</v>
       </c>
       <c r="I17" s="3">
-        <v>13400</v>
+        <v>8200</v>
       </c>
       <c r="J17" s="3">
-        <v>9600</v>
+        <v>7300</v>
       </c>
       <c r="K17" s="3">
         <v>11700</v>
@@ -1687,7 +1687,7 @@
         <v>5000</v>
       </c>
       <c r="E18" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="F18" s="3">
         <v>-100</v>
@@ -1699,10 +1699,10 @@
         <v>2000</v>
       </c>
       <c r="I18" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="J18" s="3">
-        <v>-500</v>
+        <v>1900</v>
       </c>
       <c r="K18" s="3">
         <v>4400</v>
@@ -1821,26 +1821,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1800</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1923,25 +1923,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5300</v>
+        <v>5000</v>
       </c>
       <c r="E21" s="3">
-        <v>5100</v>
+        <v>4700</v>
       </c>
       <c r="F21" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="H21" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I21" s="3">
-        <v>-700</v>
+        <v>4600</v>
       </c>
       <c r="J21" s="3">
-        <v>1300</v>
+        <v>1900</v>
       </c>
       <c r="K21" s="3">
         <v>4500</v>
@@ -2023,26 +2023,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -2427,8 +2427,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>4100</v>
       </c>
       <c r="E26" s="3">
         <v>4100</v>
@@ -2528,8 +2528,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>4100</v>
       </c>
       <c r="E27" s="3">
         <v>4100</v>
@@ -3033,26 +3033,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1800</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3134,8 +3134,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>4100</v>
       </c>
       <c r="E33" s="3">
         <v>4100</v>
@@ -3336,8 +3336,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>4100</v>
       </c>
       <c r="E35" s="3">
         <v>4100</v>
@@ -3725,10 +3725,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3819,26 +3819,26 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -4021,26 +4021,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4123,25 +4123,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>101900</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>92100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>86600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>86100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>87200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>84400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4223,23 +4223,23 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>13000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>5000</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>0</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -4325,25 +4325,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>500</v>
+        <v>1800</v>
       </c>
       <c r="E48" s="3">
-        <v>14300</v>
+        <v>1800</v>
       </c>
       <c r="F48" s="3">
-        <v>14100</v>
+        <v>1600</v>
       </c>
       <c r="G48" s="3">
-        <v>18300</v>
+        <v>1500</v>
       </c>
       <c r="H48" s="3">
-        <v>17900</v>
+        <v>1400</v>
       </c>
       <c r="I48" s="3">
-        <v>15100</v>
+        <v>1400</v>
       </c>
       <c r="J48" s="3">
-        <v>13100</v>
+        <v>1400</v>
       </c>
       <c r="K48" s="3">
         <v>1400</v>
@@ -4729,25 +4729,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10600</v>
+        <v>13300</v>
       </c>
       <c r="E52" s="3">
-        <v>12500</v>
+        <v>12800</v>
       </c>
       <c r="F52" s="3">
-        <v>13400</v>
+        <v>13500</v>
       </c>
       <c r="G52" s="3">
-        <v>13500</v>
+        <v>17900</v>
       </c>
       <c r="H52" s="3">
-        <v>13500</v>
+        <v>17600</v>
       </c>
       <c r="I52" s="3">
         <v>14800</v>
       </c>
       <c r="J52" s="3">
-        <v>16600</v>
+        <v>12700</v>
       </c>
       <c r="K52" s="3">
         <v>2600</v>
@@ -5106,25 +5106,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4400</v>
+        <v>2100</v>
       </c>
       <c r="E57" s="3">
-        <v>2600</v>
+        <v>2100</v>
       </c>
       <c r="F57" s="3">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="G57" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="H57" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I57" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="J57" s="3">
-        <v>2300</v>
+        <v>1700</v>
       </c>
       <c r="K57" s="3">
         <v>1900</v>
@@ -5308,25 +5308,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>1900</v>
       </c>
       <c r="E59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3000</v>
-      </c>
       <c r="H59" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="I59" s="3">
-        <v>2300</v>
+        <v>1900</v>
       </c>
       <c r="J59" s="3">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="K59" s="3">
         <v>5000</v>
@@ -5409,25 +5409,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5513,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
         <v>300</v>
@@ -5610,26 +5610,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -7268,8 +7268,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>4100</v>
       </c>
       <c r="E81" s="3">
         <v>4100</v>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -7422,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -8591,26 +8591,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9096,26 +9096,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F8" s="3">
         <v>19100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>19500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>12700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>8900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>10300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>12700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>23500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>18700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>7900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>10400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>9200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>11300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>8900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>9800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F9" s="3">
         <v>12500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>13000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>10900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>6700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>6600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>10500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>7000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>8200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>6700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>10500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>12300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>4000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>4300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>4200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>8400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>8400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>10300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>13300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>9100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>7700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>7800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>8200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>8200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F10" s="3">
         <v>6600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>3400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>5600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>15300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>6400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>2700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>3500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1165,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1375,14 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1361,23 +1401,23 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>5300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1385,11 +1425,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1397,26 +1437,26 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3">
         <v>5000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1424,26 +1464,32 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>200</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1451,14 +1497,14 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F17" s="3">
         <v>14100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>14900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>12800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>7800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>8200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>11700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>9500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>8200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>13400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>8100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>10000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>4300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>3100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>11800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>10100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>8800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>9100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>9300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>9500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>4400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>14000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>5300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-2900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-700</v>
       </c>
       <c r="AA18" s="3">
         <v>-800</v>
       </c>
       <c r="AB18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>2200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1882,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1842,11 +1910,11 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1858,50 +1926,50 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1917,109 +1985,121 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>4700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>14000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-5100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-2600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-600</v>
       </c>
       <c r="AA21" s="3">
         <v>-600</v>
       </c>
       <c r="AB21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>2500</v>
       </c>
-      <c r="AG21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2065,47 +2145,47 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2119,210 +2199,228 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F23" s="3">
         <v>5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>4500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>14000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
-      </c>
-      <c r="T23" s="3">
-        <v>700</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-5200</v>
       </c>
       <c r="V23" s="3">
         <v>700</v>
       </c>
       <c r="W23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="X23" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-15200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F26" s="3">
         <v>4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>16600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>10000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>1400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F27" s="3">
         <v>4100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>4100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>16600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>10000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-2200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>1400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2775,17 +2897,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2794,29 +2916,29 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>5200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>1400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>2800</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3162,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3054,11 +3194,11 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3070,50 +3210,50 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3269,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F33" s="3">
         <v>4100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>4100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>16600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>10000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-2200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>5400</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3">
         <v>100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>1400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>-900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F35" s="3">
         <v>4100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>4100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>16600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>10000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-2200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>5400</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3">
         <v>100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>1400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>-900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3784,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>40100</v>
+      </c>
+      <c r="F41" s="3">
         <v>40400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>29700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>18000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>16700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>20000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>12400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>12900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>15900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>27300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>30300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>23300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>24800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>15400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>15700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>17100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>17500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>14200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>15600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>14000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>15100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>10900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>13900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>13800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>13100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>11800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>10800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3725,17 +3905,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3814,28 +3994,34 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
@@ -3843,8 +4029,8 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3882,142 +4068,154 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>8</v>
+      <c r="Y43" s="3">
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB43" s="3">
         <v>5700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>5500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>5900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>5900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>6900</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>6400</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>5900</v>
       </c>
       <c r="AG43" s="3">
         <v>6400</v>
       </c>
       <c r="AH43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>7200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>63400</v>
+      </c>
+      <c r="F44" s="3">
         <v>60300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>66000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>68100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>63900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>63400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>65600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>70700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>70000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>68600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>67200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>64800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>61800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>61300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>55600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>55600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>53900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>57200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>53400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>54100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>54200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>55500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>57800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>58700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>59000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>59200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>58900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>58300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>55900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>55400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>56100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>57200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4042,11 +4240,11 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4117,38 +4315,44 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>104500</v>
+      </c>
+      <c r="F46" s="3">
         <v>101900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>97200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>92100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>86600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>86100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>87200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>84400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4218,8 +4422,14 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,83 +4454,89 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>9000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>9000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>100</v>
-      </c>
-      <c r="N47" s="3">
-        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>100</v>
       </c>
       <c r="P47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T47" s="3">
         <v>100</v>
       </c>
       <c r="U47" s="3">
+        <v>300</v>
+      </c>
+      <c r="V47" s="3">
         <v>100</v>
       </c>
-      <c r="V47" s="3">
-        <v>300</v>
-      </c>
       <c r="W47" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X47" s="3">
         <v>300</v>
       </c>
       <c r="Y47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA47" s="3">
         <v>17500</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>9700</v>
       </c>
       <c r="AB47" s="3">
         <v>9700</v>
       </c>
       <c r="AC47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AE47" s="3">
         <v>18500</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="3">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4331,16 +4547,16 @@
         <v>1800</v>
       </c>
       <c r="F48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H48" s="3">
         <v>1600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1500</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1400</v>
       </c>
       <c r="J48" s="3">
         <v>1400</v>
@@ -4352,76 +4568,82 @@
         <v>1400</v>
       </c>
       <c r="M48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O48" s="3">
         <v>10400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>11200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>11200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>13600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>19000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>19100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>18900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>18600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>17700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>17000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>17100</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB48" s="3">
         <v>9000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>9200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>9500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>9700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>19700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>20000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>20300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>20600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>20700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4521,8 +4743,14 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F52" s="3">
         <v>13300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>12800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>17900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>17600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>14800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>5700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>7000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>11100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>11600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>11600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>5500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>4800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>5000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>17400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>8700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>8700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>9500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>10700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>129100</v>
+      </c>
+      <c r="F54" s="3">
         <v>127000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>122800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>119000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>117800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>116900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>115900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>113100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>96200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>96800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>94900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>105100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>104900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>101100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>97400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>95900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>95700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>100000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>96700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>97300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>95600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>100100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>100500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>104500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>104600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>106700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>106200</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>105800</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>107000</v>
       </c>
       <c r="AF54" s="3">
         <v>105800</v>
       </c>
       <c r="AG54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>105800</v>
+      </c>
+      <c r="AI54" s="3">
         <v>106700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>109500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5360,117 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="E57" s="3">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="F57" s="3">
         <v>2100</v>
       </c>
       <c r="G57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1700</v>
       </c>
       <c r="K57" s="3">
         <v>1900</v>
       </c>
       <c r="L57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1300</v>
       </c>
       <c r="S57" s="3">
         <v>2000</v>
       </c>
       <c r="T57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V57" s="3">
         <v>2500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>3100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>3000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>7000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>8400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>9200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>6500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>7000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>7000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5302,68 +5570,74 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>7400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5376,65 +5650,71 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
         <v>100</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
       <c r="AE59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
         <v>500</v>
       </c>
       <c r="AH59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>1600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F60" s="3">
         <v>4800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5504,8 +5784,14 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5513,89 +5799,89 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>3400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>5200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>5800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>5500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>600</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -5605,8 +5891,14 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5631,11 +5923,11 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5647,67 +5939,73 @@
         <v>0</v>
       </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>6400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>6900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>7000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>9000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>14400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>9700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>10800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>10700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>11000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>13700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>4800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>11800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>10800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>10400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>13700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>14600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>7000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>16500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>16900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>19700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>19100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>21200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>20300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>19500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>21800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>25600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>91400</v>
+      </c>
+      <c r="F72" s="3">
         <v>87400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>83300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>79200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>79100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>78000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>76600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>76900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>60400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>56700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>54800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>53600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>52700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>49300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>47700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>43800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>44500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>43700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>43100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>47000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>46700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>48900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>49100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>47600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>47600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>47100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>47500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>45600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>48500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>48200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>46800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>47700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>126000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>125100</v>
+      </c>
+      <c r="F76" s="3">
         <v>122200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>118100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>113800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>113500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>112400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>111000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>107400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>89000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>85300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>83200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>95200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>94100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>90700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>88900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>83400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>82000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>85400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>84600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>90400</v>
-      </c>
-      <c r="W76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="X76" s="3">
-        <v>89900</v>
       </c>
       <c r="Y76" s="3">
         <v>89800</v>
       </c>
       <c r="Z76" s="3">
+        <v>89900</v>
+      </c>
+      <c r="AA76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="AB76" s="3">
         <v>88000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>87800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>87000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>87100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>84600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>86700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>86400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>84800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>83900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F81" s="3">
         <v>4100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>4100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>16600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>10000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-2200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>5400</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="3">
         <v>100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>1400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>-900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7797,10 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7410,26 +7808,26 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7440,25 +7838,25 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
       <c r="R83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -7470,25 +7868,25 @@
         <v>100</v>
       </c>
       <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>300</v>
       </c>
       <c r="AB83" s="3">
         <v>300</v>
       </c>
       <c r="AC83" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="AD83" s="3">
         <v>300</v>
       </c>
       <c r="AE83" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="AF83" s="3">
         <v>300</v>
@@ -7500,10 +7898,16 @@
         <v>300</v>
       </c>
       <c r="AI83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F89" s="3">
         <v>10700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1500</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>14100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>7400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>11200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-2700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>1300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>2800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,8 +8585,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8157,16 +8599,16 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -8175,20 +8617,20 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8226,28 +8668,34 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,8 +8902,14 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8457,20 +8917,20 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>4900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -8478,23 +8938,23 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
@@ -8517,40 +8977,46 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>0</v>
-      </c>
       <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +9052,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,11 +9080,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8687,8 +9155,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9476,14 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9011,88 +9503,94 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-25600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>2900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,11 +9615,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9192,105 +9690,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>10700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>12200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-5100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-11600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>7100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>3000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-3000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1700</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>1100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -656,480 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E8" s="3">
         <v>7500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>9200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E9" s="3">
         <v>5200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>6600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>8400</v>
       </c>
       <c r="AC9" s="3">
         <v>8400</v>
       </c>
       <c r="AD9" s="3">
+        <v>8400</v>
+      </c>
+      <c r="AE9" s="3">
         <v>10300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>13300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>7700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>7800</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>8200</v>
       </c>
       <c r="AJ9" s="3">
         <v>8200</v>
       </c>
       <c r="AK9" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AL9" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>15300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-4400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1407,20 +1426,20 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1431,8 +1450,8 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1443,58 +1462,61 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>5000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2900</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>200</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1503,11 +1525,11 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
@@ -1595,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E17" s="3">
         <v>7100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>13400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>11800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,13 +1916,14 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>8</v>
@@ -1916,8 +1949,8 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1932,46 +1965,46 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>100</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" s="3">
         <v>0</v>
@@ -1991,82 +2024,85 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E21" s="3">
         <v>500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>14000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>-600</v>
       </c>
       <c r="AB21" s="3">
         <v>-600</v>
@@ -2075,31 +2111,34 @@
         <v>-600</v>
       </c>
       <c r="AD21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2500</v>
       </c>
-      <c r="AI21" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3">
         <v>600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2151,14 +2190,14 @@
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
@@ -2166,8 +2205,8 @@
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2175,20 +2214,20 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2205,222 +2244,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-900</v>
-      </c>
-      <c r="AB23" s="3">
-        <v>-700</v>
       </c>
       <c r="AC23" s="3">
         <v>-700</v>
       </c>
       <c r="AD23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-15200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>-200</v>
       </c>
       <c r="AD24" s="3">
         <v>-200</v>
       </c>
       <c r="AE24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-300</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>100</v>
       </c>
       <c r="AG24" s="3">
         <v>100</v>
       </c>
       <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>4100</v>
       </c>
       <c r="G26" s="3">
         <v>4100</v>
       </c>
       <c r="H26" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>4100</v>
       </c>
       <c r="G27" s="3">
         <v>4100</v>
       </c>
       <c r="H27" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2903,14 +2963,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2922,26 +2982,26 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>5200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>1400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>2800</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2954,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,13 +3234,16 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>8</v>
@@ -3200,8 +3269,8 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3216,46 +3285,46 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>-100</v>
       </c>
       <c r="AE32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AF32" s="3">
         <v>0</v>
@@ -3275,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>4100</v>
       </c>
       <c r="G33" s="3">
         <v>4100</v>
       </c>
       <c r="H33" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5400</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="3">
         <v>100</v>
       </c>
       <c r="AE33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>4100</v>
       </c>
       <c r="G35" s="3">
         <v>4100</v>
       </c>
       <c r="H35" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5400</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="3">
         <v>100</v>
       </c>
       <c r="AE35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E41" s="3">
         <v>36900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>21800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>30300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>17100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>17500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>15600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>14200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3911,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>5000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -4000,25 +4089,28 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
@@ -4026,14 +4118,14 @@
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -4074,148 +4166,154 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC43" s="3">
         <v>5700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5500</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>5900</v>
       </c>
       <c r="AE43" s="3">
         <v>5900</v>
       </c>
       <c r="AF43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AG43" s="3">
         <v>6900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E44" s="3">
         <v>65100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>63400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>60300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>66000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>63900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>63400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>65600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>70700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>70000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>68600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>67200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>64800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>61800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>61300</v>
-      </c>
-      <c r="S44" s="3">
-        <v>55600</v>
       </c>
       <c r="T44" s="3">
         <v>55600</v>
       </c>
       <c r="U44" s="3">
+        <v>55600</v>
+      </c>
+      <c r="V44" s="3">
         <v>53900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>57200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>53400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>54100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>54200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>55500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>57800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>58700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>59000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>59200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>58900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>58300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>55900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>55400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>56100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>57200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4246,8 +4344,8 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4321,41 +4419,44 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E46" s="3">
         <v>103100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>104500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>101900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>97200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>92100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>86600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>86100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>84400</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4428,8 +4529,11 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,41 +4564,41 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>9000</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>9000</v>
       </c>
       <c r="O47" s="3">
+        <v>9000</v>
+      </c>
+      <c r="P47" s="3">
         <v>100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>300</v>
-      </c>
-      <c r="V47" s="3">
-        <v>100</v>
       </c>
       <c r="W47" s="3">
         <v>100</v>
       </c>
       <c r="X47" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y47" s="3">
         <v>300</v>
@@ -4503,10 +4607,10 @@
         <v>300</v>
       </c>
       <c r="AA47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB47" s="3">
         <v>17500</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>9700</v>
       </c>
       <c r="AC47" s="3">
         <v>9700</v>
@@ -4515,33 +4619,36 @@
         <v>9700</v>
       </c>
       <c r="AE47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AF47" s="3">
         <v>18500</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
         <v>200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E48" s="3">
         <v>1800</v>
@@ -4553,13 +4660,13 @@
         <v>1800</v>
       </c>
       <c r="H48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I48" s="3">
         <v>1600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1500</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1400</v>
       </c>
       <c r="K48" s="3">
         <v>1400</v>
@@ -4574,76 +4681,79 @@
         <v>1400</v>
       </c>
       <c r="O48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P48" s="3">
         <v>10400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>11200</v>
       </c>
       <c r="Q48" s="3">
         <v>11200</v>
       </c>
       <c r="R48" s="3">
+        <v>11200</v>
+      </c>
+      <c r="S48" s="3">
         <v>13600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC48" s="3">
         <v>9000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>19700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>20000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>20300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>20700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4749,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E52" s="3">
         <v>14900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1500</v>
       </c>
       <c r="Q52" s="3">
         <v>1500</v>
       </c>
       <c r="R52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S52" s="3">
         <v>2800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>7000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11100</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>11600</v>
       </c>
       <c r="Z52" s="3">
         <v>11600</v>
       </c>
       <c r="AA52" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AB52" s="3">
         <v>5500</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>4800</v>
       </c>
       <c r="AC52" s="3">
         <v>4800</v>
       </c>
       <c r="AD52" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE52" s="3">
         <v>5000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>17400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4800</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>8700</v>
       </c>
       <c r="AH52" s="3">
         <v>8700</v>
       </c>
       <c r="AI52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>10700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E54" s="3">
         <v>128900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>129100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>127000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>122800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>116900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>115900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>113100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>96200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>96800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>94900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>105100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>104900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>101100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>97400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>95900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>95700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>96700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>97300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>100100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>100500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>104500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>104600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>106700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>106200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>105800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>107000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>105800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>106700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>109500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,19 +5491,20 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>400</v>
+        <v>1300</v>
       </c>
       <c r="E57" s="3">
         <v>400</v>
       </c>
       <c r="F57" s="3">
-        <v>2100</v>
+        <v>400</v>
       </c>
       <c r="G57" s="3">
         <v>2100</v>
@@ -5383,94 +5513,97 @@
         <v>2100</v>
       </c>
       <c r="I57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>3000</v>
       </c>
       <c r="AA57" s="3">
         <v>3000</v>
       </c>
       <c r="AB57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC57" s="3">
         <v>7000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>7300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6500</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>7000</v>
       </c>
       <c r="AJ57" s="3">
         <v>7000</v>
       </c>
       <c r="AK57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AL57" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5576,71 +5709,74 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1900</v>
       </c>
       <c r="K59" s="3">
         <v>1900</v>
       </c>
       <c r="L59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M59" s="3">
         <v>2700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2300</v>
       </c>
       <c r="Q59" s="3">
         <v>2300</v>
       </c>
       <c r="R59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S59" s="3">
         <v>2200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5656,20 +5792,20 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
         <v>100</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
       <c r="AF59" s="3">
         <v>0</v>
       </c>
       <c r="AG59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AH59" s="3">
         <v>500</v>
@@ -5678,46 +5814,49 @@
         <v>500</v>
       </c>
       <c r="AJ59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK59" s="3">
         <v>1600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5790,13 +5929,16 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5805,11 +5947,11 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -5817,74 +5959,74 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>100</v>
-      </c>
-      <c r="L61" s="3">
-        <v>300</v>
       </c>
       <c r="M61" s="3">
         <v>300</v>
       </c>
       <c r="N61" s="3">
+        <v>300</v>
+      </c>
+      <c r="O61" s="3">
         <v>2100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>600</v>
       </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
       <c r="AH61" s="3">
         <v>0</v>
       </c>
@@ -5897,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5929,8 +6074,8 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5945,67 +6090,70 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>500</v>
-      </c>
-      <c r="T62" s="3">
-        <v>3200</v>
       </c>
       <c r="U62" s="3">
         <v>3200</v>
       </c>
       <c r="V62" s="3">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="W62" s="3">
         <v>5000</v>
       </c>
       <c r="X62" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Y62" s="3">
         <v>2500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>6400</v>
       </c>
       <c r="AA62" s="3">
         <v>6400</v>
       </c>
       <c r="AB62" s="3">
+        <v>6400</v>
+      </c>
+      <c r="AC62" s="3">
         <v>6900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>14400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>10800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>10700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>11000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>13700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4000</v>
-      </c>
-      <c r="F66" s="3">
-        <v>4800</v>
       </c>
       <c r="G66" s="3">
         <v>4800</v>
       </c>
       <c r="H66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>20300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>21800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>25600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E72" s="3">
         <v>92100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>91400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>87400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>83300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>79200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>79100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>78000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>76600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>60400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>54800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>53600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>43700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>43100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>46700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>48900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>49100</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>47600</v>
       </c>
       <c r="AC72" s="3">
         <v>47600</v>
       </c>
       <c r="AD72" s="3">
+        <v>47600</v>
+      </c>
+      <c r="AE72" s="3">
         <v>47100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>47500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>45600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>48500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>48200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>46800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>47700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E76" s="3">
         <v>126000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>125100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>122200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>113800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>113500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>112400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>111000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>107400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>85300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>83200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>95200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>94100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>90700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>88900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>83400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>82000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>85400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>84600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>90400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>89800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>89900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>89800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>88000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>87800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>87000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>87100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>84600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>86700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>86400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>84800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>83900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>4100</v>
       </c>
       <c r="G81" s="3">
         <v>4100</v>
       </c>
       <c r="H81" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5400</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD81" s="3">
         <v>100</v>
       </c>
       <c r="AE81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,13 +7996,14 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -7814,11 +8012,11 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -7826,11 +8024,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7844,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -7853,31 +8051,31 @@
         <v>100</v>
       </c>
       <c r="T83" s="3">
+        <v>100</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
-      </c>
-      <c r="U83" s="3">
-        <v>100</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
       </c>
       <c r="W83" s="3">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>300</v>
       </c>
       <c r="AC83" s="3">
         <v>300</v>
@@ -7886,10 +8084,10 @@
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>1200</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>300</v>
       </c>
       <c r="AG83" s="3">
         <v>300</v>
@@ -7904,10 +8102,13 @@
         <v>300</v>
       </c>
       <c r="AK83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1500</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,32 +8806,33 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -8623,17 +8843,17 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -8674,28 +8894,31 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH91" s="3">
         <v>0</v>
       </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,32 +9134,35 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>4900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5100</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
@@ -8944,20 +9173,20 @@
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
@@ -8983,40 +9212,43 @@
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
       <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>100</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-100</v>
       </c>
       <c r="AF94" s="3">
         <v>-100</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
-      </c>
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9086,8 +9319,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9509,88 +9754,91 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>600</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
       <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9621,8 +9869,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9696,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1700</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2200</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AXR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>AXR</t>
   </si>
@@ -656,505 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F8" s="3">
         <v>17900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>11200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>7500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>11900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>19100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>19500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>12700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>12700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>16100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>23500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>16100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>18700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>7900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>5300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>2400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>8900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>10400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>11300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>8900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>9800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F9" s="3">
         <v>9900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>5700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>5200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>12500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>13000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>10900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>6300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>6700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>6600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>10500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>8200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>6700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>10500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>7500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>12300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>6600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>4300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>4000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>4200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>3100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>8400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>8400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>10300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>13300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>9100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>7800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>8200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>8200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F10" s="3">
         <v>8000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>3400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>5600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>15300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>3000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>6400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>3900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>2700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>-4400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>3500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1220,10 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1307,8 +1335,14 @@
       <c r="AM12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1420,8 +1454,14 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1452,23 +1492,23 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>5300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1476,11 +1516,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1488,26 +1528,26 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>5000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2900</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1515,26 +1555,32 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>200</v>
       </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1545,23 +1591,23 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
       </c>
       <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1646,8 +1692,14 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,234 +1736,248 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8300</v>
+      </c>
+      <c r="F17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>8800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>14100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>14900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>8300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>8200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>7300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>11700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>8100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>8700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>13400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>8100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>4100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>10000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>4300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>5100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>11800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>10100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>9100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>9300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>9500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F18" s="3">
         <v>6100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>2000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>14000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>5300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>-700</v>
       </c>
       <c r="AE18" s="3">
         <v>-800</v>
       </c>
       <c r="AF18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>2200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,22 +2017,24 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>8</v>
@@ -1989,11 +2057,11 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -2005,50 +2073,50 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
@@ -2064,121 +2132,133 @@
       <c r="AM20" s="3">
         <v>0</v>
       </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="3">
         <v>6200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>14000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>5500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>3000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-600</v>
       </c>
       <c r="AE21" s="3">
         <v>-600</v>
       </c>
       <c r="AF21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>2500</v>
       </c>
-      <c r="AK21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="3">
         <v>600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2236,47 +2316,47 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>8</v>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AI22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2290,234 +2370,252 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F23" s="3">
         <v>6600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>5300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>5000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>4500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>14000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>4400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>5400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1100</v>
-      </c>
-      <c r="X23" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-5200</v>
       </c>
       <c r="Z23" s="3">
         <v>700</v>
       </c>
       <c r="AA23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>2200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-15200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>-300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,234 +2727,252 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>4000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>16600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>10000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>1400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>4100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>4100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>16600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>10000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>1400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3084,14 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3030,17 +3152,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -3049,29 +3171,29 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>5200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>1400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>2800</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3081,8 +3203,14 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3322,14 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,22 +3441,28 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>8</v>
@@ -3345,11 +3485,11 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3361,50 +3501,50 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
@@ -3420,121 +3560,133 @@
       <c r="AM32" s="3">
         <v>0</v>
       </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>4100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>4100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>16600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>10000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>5400</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>1400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,239 +3798,257 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>4100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>4100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>16600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>10000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>5400</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>1400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4088,10 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,121 +4131,129 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>44600</v>
+      </c>
+      <c r="F41" s="3">
         <v>48900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>39500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>36900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>40100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>40400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>29700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>21800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>20000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>15900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>27300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>30300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>23300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>24800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>15700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>17100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>17500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>14200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>15600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>13300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>14200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>14000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>15100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>10900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>13900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>13100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>11800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>10800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>11900</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4096,17 +4276,17 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>5000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>5000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4185,40 +4365,46 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
@@ -4226,8 +4412,8 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -4265,154 +4451,166 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
+      <c r="AC43" s="3">
+        <v>0</v>
       </c>
       <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF43" s="3">
         <v>5700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>5500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>5900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>5900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>6900</v>
-      </c>
-      <c r="AI43" s="3">
-        <v>6400</v>
-      </c>
-      <c r="AJ43" s="3">
-        <v>5900</v>
       </c>
       <c r="AK43" s="3">
         <v>6400</v>
       </c>
       <c r="AL43" s="3">
+        <v>5900</v>
+      </c>
+      <c r="AM43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="AN43" s="3">
         <v>7200</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>68600</v>
+      </c>
+      <c r="F44" s="3">
         <v>64800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>66800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>65100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>63400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>60300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>66000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>68100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>63900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>63400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>65600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>70700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>70000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>68600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>67200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>64800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>61800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>61300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>55600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>55600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>53900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>57200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>53400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>54100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>54200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>55500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>57800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>58700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>59000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>59200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>58900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>58300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>55900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>55400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>56100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>57200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4449,11 +4647,11 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4524,50 +4722,56 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>117900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>114200</v>
+      </c>
+      <c r="F46" s="3">
         <v>115000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>107500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>103100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>104500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>101900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>97200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>92100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>86600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>86100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>87200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>84400</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4637,8 +4841,14 @@
       <c r="AM46" s="3">
         <v>0</v>
       </c>
+      <c r="AN46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4675,83 +4885,89 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>9000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>9000</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>100</v>
-      </c>
-      <c r="R47" s="3">
-        <v>300</v>
       </c>
       <c r="S47" s="3">
         <v>100</v>
       </c>
       <c r="T47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="U47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X47" s="3">
         <v>100</v>
       </c>
       <c r="Y47" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z47" s="3">
         <v>100</v>
       </c>
-      <c r="Z47" s="3">
-        <v>300</v>
-      </c>
       <c r="AA47" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AB47" s="3">
         <v>300</v>
       </c>
       <c r="AC47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE47" s="3">
         <v>17500</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>9700</v>
-      </c>
-      <c r="AE47" s="3">
-        <v>9700</v>
       </c>
       <c r="AF47" s="3">
         <v>9700</v>
       </c>
       <c r="AG47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AI47" s="3">
         <v>18500</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL47" s="3">
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3">
         <v>200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AO47" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4762,10 +4978,10 @@
         <v>2200</v>
       </c>
       <c r="F48" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="G48" s="3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="H48" s="3">
         <v>1800</v>
@@ -4774,16 +4990,16 @@
         <v>1800</v>
       </c>
       <c r="J48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L48" s="3">
         <v>1600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>1400</v>
       </c>
       <c r="N48" s="3">
         <v>1400</v>
@@ -4795,76 +5011,82 @@
         <v>1400</v>
       </c>
       <c r="Q48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S48" s="3">
         <v>10400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>11200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>13700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>19000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>19100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>18900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>18600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>17700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>17000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>17100</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF48" s="3">
         <v>9000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>9200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>9500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>9700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>19700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>20000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>20300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>20600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>20700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4976,8 +5198,14 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5317,14 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5436,133 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F52" s="3">
         <v>16200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>15100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>14900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>13300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>13500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>17900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>17600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>14800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>2800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>5700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>6500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>6800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>7000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>11100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>11600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>11600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>5500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>4800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>4800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>5000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>17400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>4800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>8700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>9500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>10700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5674,133 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>140100</v>
+      </c>
+      <c r="F54" s="3">
         <v>140700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>133800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>128900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>129100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>127000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>122800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>119000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>117800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>116900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>115900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>113100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>96200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>96800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>94900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>105100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>104900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>101100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>97400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>95900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>95700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>100000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>96700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>97300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>95600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>100100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>100500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>104500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>104600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>106700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>106200</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>105800</v>
-      </c>
-      <c r="AI54" s="3">
-        <v>107000</v>
       </c>
       <c r="AJ54" s="3">
         <v>105800</v>
       </c>
       <c r="AK54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="AL54" s="3">
+        <v>105800</v>
+      </c>
+      <c r="AM54" s="3">
         <v>106700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>109500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +5840,10 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,121 +5883,129 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2100</v>
       </c>
       <c r="J57" s="3">
         <v>2100</v>
       </c>
       <c r="K57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M57" s="3">
         <v>700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
-      </c>
-      <c r="M57" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1700</v>
       </c>
       <c r="O57" s="3">
         <v>1900</v>
       </c>
       <c r="P57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
-      </c>
-      <c r="U57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>1300</v>
       </c>
       <c r="W57" s="3">
         <v>2000</v>
       </c>
       <c r="X57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z57" s="3">
         <v>2500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>3100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>3500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>2500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>3000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>7000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>7800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>8400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>2800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>9200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>6500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>7000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>7000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5849,80 +6117,86 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>7400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>2300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>2200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>2500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>2800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>2700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5935,77 +6209,83 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="3">
         <v>100</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>0</v>
-      </c>
       <c r="AI59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AJ59" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AK59" s="3">
         <v>500</v>
       </c>
       <c r="AL59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AM59" s="3">
+        <v>500</v>
+      </c>
+      <c r="AN59" s="3">
         <v>1600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F60" s="3">
         <v>5900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>5500</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6075,8 +6355,14 @@
       <c r="AM60" s="3">
         <v>0</v>
       </c>
+      <c r="AN60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6084,101 +6370,101 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>5700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>5500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>3900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>1000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>2600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>2000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>2100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>1800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>600</v>
       </c>
-      <c r="AI61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
       <c r="AK61" s="3">
         <v>0</v>
       </c>
@@ -6188,8 +6474,14 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6226,11 +6518,11 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -6242,67 +6534,73 @@
         <v>0</v>
       </c>
       <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>3200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>5000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>5000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>6400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>6400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>6900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>7000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>9000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>14400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>9700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>10700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>11000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>13700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +6712,14 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +6831,14 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +6950,133 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F66" s="3">
         <v>5900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>11500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>10800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>10400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>8500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>12500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>13700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>14600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>12000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>7000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>5800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>10200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>10700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>16500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>16900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>19700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>19100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>21200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>19500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>21800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>25600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7116,10 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7231,14 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7350,14 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7469,14 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7588,133 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>101900</v>
+      </c>
+      <c r="F72" s="3">
         <v>100700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>96000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>92100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>91400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>87400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>83300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>79200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>79100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>78000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>76600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>76900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>60400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>56700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>54800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>53600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>52700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>49300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>47700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>43800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>44500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>43700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>43100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>47000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>46700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>48900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>49100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>47600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>47600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>47100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>47500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>45600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>48500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>48200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>46800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>47700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>47500</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +7826,14 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +7945,14 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8064,133 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>139400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>136000</v>
+      </c>
+      <c r="F76" s="3">
         <v>134700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>130000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>126000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>125100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>122200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>118100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>113800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>113500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>112400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>111000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>107400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>89000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>85300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>83200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>95200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>94100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>90700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>88900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>83400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>82000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>85400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>84600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>90400</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>89800</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>89900</v>
       </c>
       <c r="AC76" s="3">
         <v>89800</v>
       </c>
       <c r="AD76" s="3">
+        <v>89900</v>
+      </c>
+      <c r="AE76" s="3">
+        <v>89800</v>
+      </c>
+      <c r="AF76" s="3">
         <v>88000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>87800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>87000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>87100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>84600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>86700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>86400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>84800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>83900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>83700</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,239 +8302,257 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>4100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>4100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>16600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>10000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>5400</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>1400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,8 +8592,10 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8205,38 +8603,38 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
       <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -8247,25 +8645,25 @@
         <v>0</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W83" s="3">
         <v>100</v>
       </c>
       <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>100</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>100</v>
@@ -8277,25 +8675,25 @@
         <v>100</v>
       </c>
       <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>-200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>300</v>
       </c>
       <c r="AF83" s="3">
         <v>300</v>
       </c>
       <c r="AG83" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="AH83" s="3">
         <v>300</v>
       </c>
       <c r="AI83" s="3">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="AJ83" s="3">
         <v>300</v>
@@ -8307,10 +8705,16 @@
         <v>300</v>
       </c>
       <c r="AM83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AN83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AO83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +8826,14 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +8945,14 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9064,14 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9183,14 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9302,133 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F89" s="3">
         <v>9500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>10700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>14100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>11200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>2600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>1300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>2800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,8 +9468,10 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9037,13 +9479,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -9052,16 +9494,16 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -9070,20 +9512,20 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -9121,28 +9563,34 @@
         <v>0</v>
       </c>
       <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-200</v>
       </c>
-      <c r="AL91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +9702,14 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,8 +9821,14 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9376,32 +9836,32 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>4900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -9409,23 +9869,23 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
@@ -9448,40 +9908,46 @@
         <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
         <v>100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
       <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
-      </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-200</v>
       </c>
-      <c r="AL94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +9987,10 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9559,11 +10027,11 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9634,8 +10102,14 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10221,14 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10340,14 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,8 +10459,14 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10006,88 +10498,94 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-25600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-4000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>1800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>600</v>
       </c>
-      <c r="AI100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
       <c r="AK100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10124,11 +10622,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10199,117 +10697,129 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F102" s="3">
         <v>9500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>10700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>12200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-5100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>7600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-11600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-3000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>9400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>3000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1700</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>2200</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>1300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>1100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>600</v>
       </c>
     </row>
